--- a/test-cases/login-test-cases.xlsx
+++ b/test-cases/login-test-cases.xlsx
@@ -877,7 +877,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -892,9 +892,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1453,25 +1450,25 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" spans="1:7">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1494,7 +1491,7 @@
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1517,7 +1514,7 @@
       <c r="F3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1540,7 +1537,7 @@
       <c r="F4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1563,7 +1560,7 @@
       <c r="F5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1586,7 +1583,7 @@
       <c r="F6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1609,7 +1606,7 @@
       <c r="F7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1632,396 +1629,396 @@
       <c r="F8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
+      <c r="A33" s="7"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
+      <c r="A34" s="7"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
+      <c r="A35" s="7"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="8"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
+      <c r="A37" s="7"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="8"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
+      <c r="A38" s="7"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="8"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
+      <c r="A39" s="7"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="8"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
+      <c r="A40" s="7"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="8"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="8"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8"/>
+      <c r="A42" s="7"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="8"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
+      <c r="A43" s="7"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="8"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8"/>
+      <c r="A44" s="7"/>
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="8"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
+      <c r="A45" s="7"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="8"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
+      <c r="A46" s="7"/>
+      <c r="B46" s="7"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="8"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
+      <c r="A47" s="7"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="8"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8"/>
+      <c r="A48" s="7"/>
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="8"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
-      <c r="G49" s="8"/>
+      <c r="A49" s="7"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="7"/>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="8"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="8"/>
+      <c r="A50" s="7"/>
+      <c r="B50" s="7"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="7"/>
+      <c r="G50" s="7"/>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="8"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
-      <c r="G51" s="8"/>
+      <c r="A51" s="7"/>
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2099,7 +2096,7 @@
       <c r="F3" s="2"/>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -2147,7 +2144,7 @@
       <c r="F6" s="2"/>
     </row>
     <row r="7" ht="74" customHeight="1" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -2163,7 +2160,7 @@
       <c r="F7" s="2"/>
     </row>
     <row r="8" ht="42.75" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B8" s="3" t="s">

--- a/test-cases/login-test-cases.xlsx
+++ b/test-cases/login-test-cases.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17580"/>
+    <workbookView windowHeight="17580" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases" sheetId="2" r:id="rId1"/>
@@ -253,11 +253,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;฿&quot;* #,##0.00_-;\-&quot;฿&quot;* #,##0.00_-;_-&quot;฿&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-&quot;฿&quot;* #,##0_-;\-&quot;฿&quot;* #,##0_-;_-&quot;฿&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="180" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -877,7 +878,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -891,6 +892,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1450,25 +1454,25 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" spans="1:7">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1491,7 +1495,7 @@
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="7" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1514,7 +1518,7 @@
       <c r="F3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1537,7 +1541,7 @@
       <c r="F4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="7" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1560,7 +1564,7 @@
       <c r="F5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="7" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1583,7 +1587,7 @@
       <c r="F6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="7" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1606,7 +1610,7 @@
       <c r="F7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="7" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1629,396 +1633,396 @@
       <c r="F8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
+      <c r="A32" s="8"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="7"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
+      <c r="A34" s="8"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="7"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="7"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
+      <c r="A36" s="8"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="7"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
+      <c r="A37" s="8"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="7"/>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
+      <c r="A38" s="8"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="7"/>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
+      <c r="A39" s="8"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="7"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
+      <c r="A40" s="8"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
+      <c r="A41" s="8"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="7"/>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
+      <c r="A42" s="8"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="7"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="7"/>
+      <c r="A43" s="8"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="7"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
+      <c r="A44" s="8"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="7"/>
-      <c r="B45" s="7"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="7"/>
+      <c r="A45" s="8"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="7"/>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
+      <c r="A46" s="8"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="7"/>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="7"/>
+      <c r="A47" s="8"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="7"/>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
+      <c r="A48" s="8"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8"/>
+      <c r="G48" s="8"/>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="7"/>
-      <c r="B49" s="7"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
-      <c r="G49" s="7"/>
+      <c r="A49" s="8"/>
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="8"/>
+      <c r="G49" s="8"/>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="7"/>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
+      <c r="A50" s="8"/>
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="7"/>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
+      <c r="A51" s="8"/>
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2077,7 +2081,9 @@
         <v>50</v>
       </c>
       <c r="E2" s="4"/>
-      <c r="F2" s="2"/>
+      <c r="F2" s="5">
+        <v>46304</v>
+      </c>
     </row>
     <row r="3" ht="64" customHeight="1" spans="1:6">
       <c r="A3" s="2" t="s">
@@ -2093,9 +2099,11 @@
         <v>52</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" ht="44" customHeight="1" spans="1:6">
+      <c r="F3" s="5">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="4" ht="67" customHeight="1" spans="1:6">
       <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
@@ -2109,9 +2117,11 @@
         <v>54</v>
       </c>
       <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" ht="45" customHeight="1" spans="1:6">
+      <c r="F4" s="5">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="5" ht="62" customHeight="1" spans="1:6">
       <c r="A5" s="2" t="s">
         <v>25</v>
       </c>
@@ -2125,9 +2135,11 @@
         <v>56</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" ht="45" customHeight="1" spans="1:6">
+      <c r="F5" s="5">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="6" ht="65" customHeight="1" spans="1:6">
       <c r="A6" s="2" t="s">
         <v>29</v>
       </c>
@@ -2141,7 +2153,9 @@
         <v>57</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+      <c r="F6" s="5">
+        <v>46304</v>
+      </c>
     </row>
     <row r="7" ht="74" customHeight="1" spans="1:6">
       <c r="A7" s="2" t="s">
@@ -2157,9 +2171,11 @@
         <v>59</v>
       </c>
       <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" ht="42.75" spans="1:6">
+      <c r="F7" s="5">
+        <v>46305</v>
+      </c>
+    </row>
+    <row r="8" ht="59" customHeight="1" spans="1:6">
       <c r="A8" s="2" t="s">
         <v>39</v>
       </c>
@@ -2173,7 +2189,9 @@
         <v>61</v>
       </c>
       <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+      <c r="F8" s="5">
+        <v>46305</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test-cases/login-test-cases.xlsx
+++ b/test-cases/login-test-cases.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17580" activeTab="1"/>
+    <workbookView windowHeight="17580"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases" sheetId="2" r:id="rId1"/>
@@ -28,12 +28,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="63">
   <si>
     <t>TC ID</t>
   </si>
   <si>
     <t>Title</t>
+  </si>
+  <si>
+    <t>Test Type</t>
   </si>
   <si>
     <t>Precondition</t>
@@ -1442,18 +1445,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G51"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
+  <dimension ref="A1:H51"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="14.5" customWidth="1"/>
     <col min="2" max="2" width="28.75" customWidth="1"/>
-    <col min="3" max="3" width="28.625" customWidth="1"/>
-    <col min="4" max="4" width="36.25" customWidth="1"/>
-    <col min="5" max="5" width="42.875" customWidth="1"/>
-    <col min="6" max="6" width="34.125" customWidth="1"/>
+    <col min="3" max="3" width="16.375" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="36.25" customWidth="1"/>
+    <col min="6" max="6" width="42.875" customWidth="1"/>
+    <col min="7" max="7" width="34.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:7">
+    <row r="1" ht="15.75" spans="1:8">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1475,17 +1479,18 @@
       <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" ht="77" customHeight="1" spans="1:7">
+      <c r="H1" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="77" customHeight="1" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="C2" s="3"/>
       <c r="D2" s="3" t="s">
         <v>10</v>
       </c>
@@ -1495,22 +1500,23 @@
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" ht="76" customHeight="1" spans="1:7">
+      <c r="H2" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" ht="76" customHeight="1" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="3" t="s">
         <v>16</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>17</v>
@@ -1518,21 +1524,22 @@
       <c r="F3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" ht="81" customHeight="1" spans="1:7">
+      <c r="G3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" ht="81" customHeight="1" spans="1:8">
       <c r="A4" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E4" s="3" t="s">
@@ -1541,66 +1548,69 @@
       <c r="F4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" ht="72" customHeight="1" spans="1:7">
+      <c r="G4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" ht="72" customHeight="1" spans="1:8">
       <c r="A5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="3" t="s">
         <v>27</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" ht="72" customHeight="1" spans="1:7">
+        <v>29</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" ht="72" customHeight="1" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="3" t="s">
         <v>31</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" ht="72" customHeight="1" spans="1:7">
+        <v>33</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" ht="72" customHeight="1" spans="1:8">
       <c r="A7" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="3" t="s">
         <v>35</v>
       </c>
+      <c r="C7" s="3"/>
       <c r="D7" s="3" t="s">
         <v>36</v>
       </c>
@@ -1610,34 +1620,38 @@
       <c r="F7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" ht="61" customHeight="1" spans="1:7">
+      <c r="G7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" ht="61" customHeight="1" spans="1:8">
       <c r="A8" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="3" t="s">
         <v>41</v>
       </c>
+      <c r="C8" s="3"/>
       <c r="D8" s="3" t="s">
         <v>42</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="G8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -1645,8 +1659,9 @@
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="H9" s="8"/>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -1654,8 +1669,9 @@
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="H10" s="8"/>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -1663,8 +1679,9 @@
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="H11" s="8"/>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -1672,8 +1689,9 @@
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="H12" s="8"/>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -1681,8 +1699,9 @@
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="H13" s="8"/>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -1690,8 +1709,9 @@
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="H14" s="8"/>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -1699,8 +1719,9 @@
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
       <c r="G15" s="8"/>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="H15" s="8"/>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -1708,8 +1729,9 @@
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="H16" s="8"/>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -1717,8 +1739,9 @@
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="H17" s="8"/>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -1726,8 +1749,9 @@
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="H18" s="8"/>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -1735,8 +1759,9 @@
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="H19" s="8"/>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -1744,8 +1769,9 @@
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="H20" s="8"/>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -1753,8 +1779,9 @@
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="H21" s="8"/>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -1762,17 +1789,19 @@
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
-    </row>
-    <row r="23" spans="1:7">
+      <c r="H22" s="8"/>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="9"/>
       <c r="G23" s="8"/>
-    </row>
-    <row r="24" spans="1:7">
+      <c r="H23" s="8"/>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -1780,8 +1809,9 @@
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
-    </row>
-    <row r="25" spans="1:7">
+      <c r="H24" s="8"/>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
@@ -1789,8 +1819,9 @@
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
-    </row>
-    <row r="26" spans="1:7">
+      <c r="H25" s="8"/>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -1798,8 +1829,9 @@
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
-    </row>
-    <row r="27" spans="1:7">
+      <c r="H26" s="8"/>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -1807,8 +1839,9 @@
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
-    </row>
-    <row r="28" spans="1:7">
+      <c r="H27" s="8"/>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -1816,8 +1849,9 @@
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
       <c r="G28" s="8"/>
-    </row>
-    <row r="29" spans="1:7">
+      <c r="H28" s="8"/>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -1825,8 +1859,9 @@
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
       <c r="G29" s="8"/>
-    </row>
-    <row r="30" spans="1:7">
+      <c r="H29" s="8"/>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -1834,8 +1869,9 @@
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
       <c r="G30" s="8"/>
-    </row>
-    <row r="31" spans="1:7">
+      <c r="H30" s="8"/>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -1843,8 +1879,9 @@
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
       <c r="G31" s="8"/>
-    </row>
-    <row r="32" spans="1:7">
+      <c r="H31" s="8"/>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -1852,8 +1889,9 @@
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8"/>
-    </row>
-    <row r="33" spans="1:7">
+      <c r="H32" s="8"/>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -1861,8 +1899,9 @@
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
-    </row>
-    <row r="34" spans="1:7">
+      <c r="H33" s="8"/>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -1870,8 +1909,9 @@
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8"/>
-    </row>
-    <row r="35" spans="1:7">
+      <c r="H34" s="8"/>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -1879,8 +1919,9 @@
       <c r="E35" s="8"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
-    </row>
-    <row r="36" spans="1:7">
+      <c r="H35" s="8"/>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -1888,8 +1929,9 @@
       <c r="E36" s="8"/>
       <c r="F36" s="8"/>
       <c r="G36" s="8"/>
-    </row>
-    <row r="37" spans="1:7">
+      <c r="H36" s="8"/>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
@@ -1897,8 +1939,9 @@
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
       <c r="G37" s="8"/>
-    </row>
-    <row r="38" spans="1:7">
+      <c r="H37" s="8"/>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" s="8"/>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
@@ -1906,8 +1949,9 @@
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
       <c r="G38" s="8"/>
-    </row>
-    <row r="39" spans="1:7">
+      <c r="H38" s="8"/>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
@@ -1915,8 +1959,9 @@
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
       <c r="G39" s="8"/>
-    </row>
-    <row r="40" spans="1:7">
+      <c r="H39" s="8"/>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
@@ -1924,8 +1969,9 @@
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
       <c r="G40" s="8"/>
-    </row>
-    <row r="41" spans="1:7">
+      <c r="H40" s="8"/>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41" s="8"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
@@ -1933,8 +1979,9 @@
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
       <c r="G41" s="8"/>
-    </row>
-    <row r="42" spans="1:7">
+      <c r="H41" s="8"/>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -1942,8 +1989,9 @@
       <c r="E42" s="8"/>
       <c r="F42" s="8"/>
       <c r="G42" s="8"/>
-    </row>
-    <row r="43" spans="1:7">
+      <c r="H42" s="8"/>
+    </row>
+    <row r="43" spans="1:8">
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
@@ -1951,8 +1999,9 @@
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
       <c r="G43" s="8"/>
-    </row>
-    <row r="44" spans="1:7">
+      <c r="H43" s="8"/>
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
@@ -1960,8 +2009,9 @@
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
       <c r="G44" s="8"/>
-    </row>
-    <row r="45" spans="1:7">
+      <c r="H44" s="8"/>
+    </row>
+    <row r="45" spans="1:8">
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
@@ -1969,8 +2019,9 @@
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
       <c r="G45" s="8"/>
-    </row>
-    <row r="46" spans="1:7">
+      <c r="H45" s="8"/>
+    </row>
+    <row r="46" spans="1:8">
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
@@ -1978,8 +2029,9 @@
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
       <c r="G46" s="8"/>
-    </row>
-    <row r="47" spans="1:7">
+      <c r="H46" s="8"/>
+    </row>
+    <row r="47" spans="1:8">
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
@@ -1987,8 +2039,9 @@
       <c r="E47" s="8"/>
       <c r="F47" s="8"/>
       <c r="G47" s="8"/>
-    </row>
-    <row r="48" spans="1:7">
+      <c r="H47" s="8"/>
+    </row>
+    <row r="48" spans="1:8">
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
@@ -1996,8 +2049,9 @@
       <c r="E48" s="8"/>
       <c r="F48" s="8"/>
       <c r="G48" s="8"/>
-    </row>
-    <row r="49" spans="1:7">
+      <c r="H48" s="8"/>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
@@ -2005,8 +2059,9 @@
       <c r="E49" s="8"/>
       <c r="F49" s="8"/>
       <c r="G49" s="8"/>
-    </row>
-    <row r="50" spans="1:7">
+      <c r="H49" s="8"/>
+    </row>
+    <row r="50" spans="1:8">
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
@@ -2014,8 +2069,9 @@
       <c r="E50" s="8"/>
       <c r="F50" s="8"/>
       <c r="G50" s="8"/>
-    </row>
-    <row r="51" spans="1:7">
+      <c r="H50" s="8"/>
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
@@ -2023,10 +2079,11 @@
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
       <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" display="1. เปิด https://www.saucedemo.com/ &#10;2. กรอก Username &#10;3. กรอก Password &#10;4. คลิกปุ่ม Login" tooltip="https://www.saucedemo.com/"/>
+    <hyperlink ref="F2" r:id="rId1" display="1. เปิด https://www.saucedemo.com/ &#10;2. กรอก Username &#10;3. กรอก Password &#10;4. คลิกปุ่ม Login" tooltip="https://www.saucedemo.com/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2052,33 +2109,33 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" ht="65" customHeight="1" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="5">
@@ -2087,16 +2144,16 @@
     </row>
     <row r="3" ht="64" customHeight="1" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="5">
@@ -2105,16 +2162,16 @@
     </row>
     <row r="4" ht="67" customHeight="1" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="5">
@@ -2123,16 +2180,16 @@
     </row>
     <row r="5" ht="62" customHeight="1" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="5">
@@ -2141,16 +2198,16 @@
     </row>
     <row r="6" ht="65" customHeight="1" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="5">
@@ -2159,16 +2216,16 @@
     </row>
     <row r="7" ht="74" customHeight="1" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="5">
@@ -2177,16 +2234,16 @@
     </row>
     <row r="8" ht="59" customHeight="1" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="5">

--- a/test-cases/login-test-cases.xlsx
+++ b/test-cases/login-test-cases.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17580"/>
+    <workbookView windowWidth="25800" windowHeight="16980"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="66">
   <si>
     <t>TC ID</t>
   </si>
@@ -58,6 +58,9 @@
   </si>
   <si>
     <t>Verify Valid User Login</t>
+  </si>
+  <si>
+    <t>Positive</t>
   </si>
   <si>
     <t>ผู้ใช้ยังไม่ได้ Login และอยู่หน้า Login</t>
@@ -86,6 +89,9 @@
     <t>Verify Login with Invalid Password</t>
   </si>
   <si>
+    <t>Negative</t>
+  </si>
+  <si>
     <t>Username: standard_user Password: secret_sorce</t>
   </si>
   <si>
@@ -120,6 +126,9 @@
   <si>
     <t>1. ระบบไม่อนุญาตให้ Login
 2. ผู้ใช้ไม่สามารถเข้าสู่หน้า Products ได้</t>
+  </si>
+  <si>
+    <t>Medium</t>
   </si>
   <si>
     <t>TC-LOGIN-004</t>
@@ -881,7 +890,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -902,6 +911,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1455,6 +1467,7 @@
     <col min="5" max="5" width="36.25" customWidth="1"/>
     <col min="6" max="6" width="42.875" customWidth="1"/>
     <col min="7" max="7" width="34.125" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" spans="1:8">
@@ -1490,596 +1503,610 @@
       <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="3"/>
+      <c r="C2" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="D2" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="7" t="s">
         <v>14</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3" ht="76" customHeight="1" spans="1:8">
       <c r="A3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>15</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="4" ht="81" customHeight="1" spans="1:8">
       <c r="A4" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>18</v>
+      </c>
       <c r="D4" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>14</v>
+        <v>27</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="5" ht="72" customHeight="1" spans="1:8">
       <c r="A5" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="H5" s="8" t="s">
         <v>28</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="6" ht="72" customHeight="1" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="2"/>
+        <v>34</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>18</v>
+      </c>
       <c r="D6" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>14</v>
+        <v>27</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="7" ht="72" customHeight="1" spans="1:8">
       <c r="A7" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>18</v>
+      </c>
       <c r="D7" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>14</v>
+        <v>42</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="8" ht="61" customHeight="1" spans="1:8">
       <c r="A8" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="3"/>
+        <v>44</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>18</v>
+      </c>
       <c r="D8" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>14</v>
+        <v>21</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
+      <c r="A32" s="9"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
+      <c r="A33" s="9"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
+      <c r="A35" s="9"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
+      <c r="A36" s="9"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="8"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
+      <c r="A37" s="9"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="8"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="8"/>
+      <c r="A38" s="9"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="8"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="8"/>
+      <c r="A39" s="9"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="8"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="8"/>
+      <c r="A40" s="9"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="8"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="8"/>
+      <c r="A41" s="9"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="8"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8"/>
-      <c r="H42" s="8"/>
+      <c r="A42" s="9"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="8"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
+      <c r="A43" s="9"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="8"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8"/>
-      <c r="H44" s="8"/>
+      <c r="A44" s="9"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="8"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
+      <c r="A45" s="9"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="8"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="8"/>
+      <c r="A46" s="9"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="9"/>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="8"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="8"/>
+      <c r="A47" s="9"/>
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="9"/>
+      <c r="H47" s="9"/>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="8"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8"/>
-      <c r="H48" s="8"/>
+      <c r="A48" s="9"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="9"/>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="8"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
-      <c r="G49" s="8"/>
-      <c r="H49" s="8"/>
+      <c r="A49" s="9"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="9"/>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="8"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="8"/>
-      <c r="H50" s="8"/>
+      <c r="A50" s="9"/>
+      <c r="B50" s="9"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="9"/>
+      <c r="G50" s="9"/>
+      <c r="H50" s="9"/>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="8"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
-      <c r="G51" s="8"/>
-      <c r="H51" s="8"/>
+      <c r="A51" s="9"/>
+      <c r="B51" s="9"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="9"/>
+      <c r="F51" s="9"/>
+      <c r="G51" s="9"/>
+      <c r="H51" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2109,19 +2136,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" ht="65" customHeight="1" spans="1:6">
@@ -2129,13 +2156,13 @@
         <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="5">
@@ -2144,16 +2171,16 @@
     </row>
     <row r="3" ht="64" customHeight="1" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="5">
@@ -2162,16 +2189,16 @@
     </row>
     <row r="4" ht="67" customHeight="1" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="5">
@@ -2180,16 +2207,16 @@
     </row>
     <row r="5" ht="62" customHeight="1" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="5">
@@ -2198,16 +2225,16 @@
     </row>
     <row r="6" ht="65" customHeight="1" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="5">
@@ -2216,16 +2243,16 @@
     </row>
     <row r="7" ht="74" customHeight="1" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="5">
@@ -2234,16 +2261,16 @@
     </row>
     <row r="8" ht="59" customHeight="1" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="5">

--- a/test-cases/login-test-cases.xlsx
+++ b/test-cases/login-test-cases.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="120">
   <si>
     <t>SAUCEDEMO  /  LOGIN</t>
   </si>
@@ -202,7 +202,34 @@
     <t>secret_sorce</t>
   </si>
   <si>
-    <t>Login is rejected and the Products page is not accessible. Error: "Epic sadface: Username and password do not match any user in this service".</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Login is rejected and the Products page is not accessible. Error: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Epic sadface: Username and password do not match any user in this service</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>".</t>
+    </r>
   </si>
   <si>
     <t>Leave the Username field blank.</t>
@@ -214,13 +241,105 @@
     <t>Enter the password.</t>
   </si>
   <si>
-    <t>Login is rejected and the Products page is not accessible. Error: "Epic sadface: Username is required".</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Login is rejected and the Products page is not accessible. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Error:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> "Epic sadface: Username is required</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>".</t>
+    </r>
   </si>
   <si>
     <t>Leave the Password field blank.</t>
   </si>
   <si>
-    <t>Login is rejected and the Products page is not accessible. Error: "Epic sadface: Password is required".</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Login is rejected and the Products page is not accessible. Error: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Epic sadface: Password is required</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>".</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Login is rejected and the Products page is not accessible. Error: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Epic sadface: Username is required</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>".</t>
+    </r>
   </si>
   <si>
     <t>Open a new incognito browser window.</t>
@@ -238,7 +357,34 @@
     <t>Press Enter and observe the resulting page.</t>
   </si>
   <si>
-    <t>Unauthenticated access to /inventory.html is blocked. The user is redirected to Login and sees "Epic sadface: You can only access '/inventory.html' when you are logged in.".</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Unauthenticated access to /inventory.html is blocked. The user is redirected to Login and sees "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Epic sadface: You can only access '/inventory.html' when you are logged in.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>".</t>
+    </r>
   </si>
   <si>
     <t>Enter the locked account username.</t>
@@ -247,7 +393,34 @@
     <t>locked_out_user</t>
   </si>
   <si>
-    <t>Login is rejected and the Products page is not accessible. Error: "Epic sadface: Sorry, this user has been locked out.".</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Login is rejected and the Products page is not accessible. Error: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Epic sadface: Sorry, this user has been locked out.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>".</t>
+    </r>
   </si>
   <si>
     <t>Confirm the Products page is displayed while logged in.</t>
@@ -309,6 +482,9 @@
     <t>MANUAL QA TEST DOCUMENTATION   •   TEST EXECUTION RESULTS</t>
   </si>
   <si>
+    <t>Evidence screenshots are grouped by Test Case ID, not individually mapped to each Actual Result entry. One screenshot may support multiple observations.</t>
+  </si>
+  <si>
     <t>Actual Result</t>
   </si>
   <si>
@@ -327,8 +503,7 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>1. Login succeeded.
-2. The browser redirected to the Products page, and the product list was displayed.</t>
+    <t>1. Login succeeded.</t>
   </si>
   <si>
     <t>PASS</t>
@@ -337,56 +512,269 @@
     <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-001_PASS.png</t>
   </si>
   <si>
-    <t>1. Login was rejected.
-2. The error appeared: "Epic sadface: Username and password do not match any user in this service".</t>
+    <t>2. The browser redirected to the Products page, and the product list was displayed.</t>
+  </si>
+  <si>
+    <t>1. Login was rejected.</t>
   </si>
   <si>
     <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-002_PASS.png</t>
   </si>
   <si>
-    <t>1. Login was rejected.
-2. The error appeared: "Epic sadface: Username is required".</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2. The error appeared: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Epic sadface: Username and password do not match any user in this service</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>".</t>
+    </r>
   </si>
   <si>
     <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-003_PASS.png</t>
   </si>
   <si>
-    <t>1. Login was rejected.
-2. The error appeared: "Epic sadface: Password is required".</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2. The error appeared: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Epic sadface: Username is required</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>".</t>
+    </r>
   </si>
   <si>
     <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-004_PASS.png</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2. The error appeared: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Epic sadface: Password is required</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>".</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1. Login was rejected.
+2. The error appeared: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Epic sadface: Username is required</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>".</t>
+    </r>
+  </si>
+  <si>
     <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-005_PASS.png</t>
   </si>
   <si>
-    <t>1. Direct access to the Products page was blocked.
-2. The browser redirected to the Login page.
-3. The error appeared: "Epic sadface: You can only access '/inventory.html' when you are logged in."</t>
+    <t>1. Direct access to the Products page was blocked.</t>
   </si>
   <si>
     <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-006_PASS.png</t>
   </si>
   <si>
-    <t>1. Login was rejected.
-2. The error appeared: "Epic sadface: Sorry, this user has been locked out."</t>
+    <t>2. The browser redirected to the Login page.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3. The error appeared: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Epic sadface: You can only access '/inventory.html' when you are logged in</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>."</t>
+    </r>
   </si>
   <si>
     <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-007_PASS.png</t>
   </si>
   <si>
-    <t>1. The user was successfully logged in and the Products page was displayed.
-2. The navigation menu opened and the Logout option was available.
-3. After selecting Logout, the application returned to the Login page.
-4. Attempting to access `/inventory.html` after logout was blocked.
-5. The application displayed the error message: "Epic sadface: You can only access '/inventory.html' when you are logged in."</t>
-  </si>
-  <si>
-    <t>1. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-008_01_PRODUCTS.png
-2. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-008_02_MENU.png
-3. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-008_03_LOGIN.png
-4. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-008_04_ACCESS_BLOCKED.png</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2. The error appeared: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Epic sadface: Sorry, this user has been locked out</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>."</t>
+    </r>
+  </si>
+  <si>
+    <t>1. The user was successfully logged in and the Products page was displayed.</t>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-008_01_PRODUCTS.png</t>
+  </si>
+  <si>
+    <t>2. The navigation menu opened and the Logout option was available.</t>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-008_02_MENU.png</t>
+  </si>
+  <si>
+    <t>3. After selecting Logout, the application returned to the Login page.</t>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-008_03_LOGIN.png</t>
+  </si>
+  <si>
+    <t>4. Attempting to access `/inventory.html` after logout was blocked.</t>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-008_04_ACCESS_BLOCKED.png</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5. The application displayed the error message: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Epic sadface: You can only access '/inventory.html' when you are logged in</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>."</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -400,7 +788,7 @@
     <numFmt numFmtId="179" formatCode="_-&quot;฿&quot;* #,##0_-;\-&quot;฿&quot;* #,##0_-;_-&quot;฿&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="180" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -425,6 +813,12 @@
       <sz val="10"/>
       <color rgb="FF17365D"/>
       <name val="Aptos"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF002060"/>
+      <name val="Carlito"/>
       <charset val="134"/>
     </font>
     <font>
@@ -571,13 +965,25 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF1D3348"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Aptos"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="40">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -622,12 +1028,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7FAFD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -813,7 +1213,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -883,6 +1283,43 @@
       <bottom style="hair">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1032,31 +1469,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1065,119 +1499,122 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1200,107 +1637,179 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="6" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="6" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="6" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="7" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1308,16 +1817,19 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1375,7 +1887,17 @@
   <dxfs count="22">
     <dxf>
       <font>
-        <color theme="9"/>
+        <color theme="5"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0070C0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
       </font>
     </dxf>
     <dxf>
@@ -1385,17 +1907,7 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0070C0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="5"/>
+        <color theme="9"/>
       </font>
     </dxf>
     <dxf>
@@ -1832,44 +2344,44 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:7">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="27"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="50"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:7">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="30"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="52"/>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:7">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="31" t="s">
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="31"/>
-      <c r="F3" s="32"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="54"/>
     </row>
     <row r="4" ht="11" customHeight="1" spans="1:7">
-      <c r="A4" s="8"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="33"/>
+      <c r="A4" s="55"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="57"/>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:7">
       <c r="A5" s="10" t="s">
@@ -1890,191 +2402,191 @@
       <c r="F5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="46" t="s">
+      <c r="G5" s="70" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" ht="50" customHeight="1" spans="1:7">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="71" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="48" t="s">
+      <c r="C6" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="48" t="s">
+      <c r="D6" s="72" t="s">
         <v>14</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="48" t="s">
+      <c r="F6" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="49" t="s">
+      <c r="G6" s="73" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" ht="50" customHeight="1" spans="1:7">
-      <c r="A7" s="40" t="s">
+      <c r="A7" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C7" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="41" t="s">
+      <c r="D7" s="64" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="41" t="s">
+      <c r="F7" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="49" t="s">
+      <c r="G7" s="74" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="8" ht="50" customHeight="1" spans="1:7">
-      <c r="A8" s="47" t="s">
+      <c r="A8" s="71" t="s">
         <v>21</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="48" t="s">
+      <c r="C8" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="48" t="s">
+      <c r="D8" s="72" t="s">
         <v>20</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="48" t="s">
+      <c r="F8" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="49" t="s">
+      <c r="G8" s="73" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="9" ht="50" customHeight="1" spans="1:7">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="41" t="s">
+      <c r="C9" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="41" t="s">
+      <c r="D9" s="64" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="41" t="s">
+      <c r="F9" s="64" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="49" t="s">
+      <c r="G9" s="74" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="10" ht="50" customHeight="1" spans="1:7">
-      <c r="A10" s="47" t="s">
+      <c r="A10" s="71" t="s">
         <v>27</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="48" t="s">
+      <c r="C10" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="48" t="s">
+      <c r="D10" s="72" t="s">
         <v>20</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="48" t="s">
+      <c r="F10" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="49" t="s">
+      <c r="G10" s="73" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" ht="50" customHeight="1" spans="1:7">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="41" t="s">
+      <c r="C11" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="41" t="s">
+      <c r="D11" s="64" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="41" t="s">
+      <c r="F11" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="49" t="s">
+      <c r="G11" s="74" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="12" ht="50" customHeight="1" spans="1:7">
-      <c r="A12" s="47" t="s">
+      <c r="A12" s="71" t="s">
         <v>33</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="48" t="s">
+      <c r="C12" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="48" t="s">
+      <c r="D12" s="72" t="s">
         <v>20</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="F12" s="48" t="s">
+      <c r="F12" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="49" t="s">
+      <c r="G12" s="73" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="13" ht="49" customHeight="1" spans="1:7">
-      <c r="A13" s="40" t="s">
+      <c r="A13" s="63" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="41" t="s">
+      <c r="C13" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="41" t="s">
+      <c r="D13" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="41" t="s">
+      <c r="F13" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="G13" s="49" t="s">
+      <c r="G13" s="74" t="s">
         <v>39</v>
       </c>
     </row>
@@ -2109,40 +2621,40 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:5">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="27"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="50"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:5">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="30"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="52"/>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:5">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="6"/>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="32"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="54"/>
     </row>
     <row r="4" ht="11" customHeight="1" spans="1:5">
-      <c r="A4" s="8"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="33"/>
+      <c r="A4" s="55"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="57"/>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5">
       <c r="A5" s="10" t="s">
@@ -2162,484 +2674,484 @@
       </c>
     </row>
     <row r="6" ht="29" customHeight="1" spans="1:5">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="35">
+      <c r="B6" s="59">
         <v>1</v>
       </c>
-      <c r="C6" s="36" t="s">
+      <c r="C6" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="37" t="s">
+      <c r="D6" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="38" t="s">
+      <c r="E6" s="61" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="7" ht="29" customHeight="1" spans="1:5">
-      <c r="A7" s="39"/>
-      <c r="B7" s="35">
+      <c r="A7" s="62"/>
+      <c r="B7" s="59">
         <v>2</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="38" t="s">
+      <c r="D7" s="61" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="38" t="s">
+      <c r="E7" s="61" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="8" ht="29" customHeight="1" spans="1:5">
-      <c r="A8" s="39"/>
-      <c r="B8" s="35">
+      <c r="A8" s="62"/>
+      <c r="B8" s="59">
         <v>3</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="D8" s="61" t="s">
         <v>51</v>
       </c>
-      <c r="E8" s="38" t="s">
+      <c r="E8" s="61" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1" spans="1:5">
-      <c r="A9" s="39"/>
-      <c r="B9" s="35">
+      <c r="A9" s="62"/>
+      <c r="B9" s="59">
         <v>4</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="38" t="s">
+      <c r="D9" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="38" t="s">
+      <c r="E9" s="61" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="10" ht="29" customHeight="1" spans="1:5">
-      <c r="A10" s="40" t="s">
+      <c r="A10" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="41">
+      <c r="B10" s="64">
         <v>1</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="42" t="s">
+      <c r="D10" s="65" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="43" t="s">
+      <c r="E10" s="66" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="11" ht="29" customHeight="1" spans="1:5">
-      <c r="A11" s="21"/>
-      <c r="B11" s="41">
+      <c r="A11" s="67"/>
+      <c r="B11" s="64">
         <v>2</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="43" t="s">
+      <c r="D11" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="E11" s="43" t="s">
+      <c r="E11" s="66" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="12" ht="29" customHeight="1" spans="1:5">
-      <c r="A12" s="21"/>
-      <c r="B12" s="41">
+      <c r="A12" s="67"/>
+      <c r="B12" s="64">
         <v>3</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="D12" s="43" t="s">
+      <c r="D12" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="E12" s="43" t="s">
+      <c r="E12" s="66" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1" spans="1:5">
-      <c r="A13" s="21"/>
-      <c r="B13" s="41">
+      <c r="A13" s="67"/>
+      <c r="B13" s="64">
         <v>4</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="43" t="s">
+      <c r="D13" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="E13" s="43" t="s">
+      <c r="E13" s="66" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="14" ht="29" customHeight="1" spans="1:5">
-      <c r="A14" s="34" t="s">
+      <c r="A14" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="35">
+      <c r="B14" s="59">
         <v>1</v>
       </c>
-      <c r="C14" s="36" t="s">
+      <c r="C14" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="37" t="s">
+      <c r="D14" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="38" t="s">
+      <c r="E14" s="61" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="15" ht="29" customHeight="1" spans="1:5">
-      <c r="A15" s="39"/>
-      <c r="B15" s="35">
+      <c r="A15" s="62"/>
+      <c r="B15" s="59">
         <v>2</v>
       </c>
-      <c r="C15" s="36" t="s">
+      <c r="C15" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="38" t="s">
+      <c r="D15" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="38" t="s">
+      <c r="E15" s="61" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="16" ht="29" customHeight="1" spans="1:5">
-      <c r="A16" s="39"/>
-      <c r="B16" s="35">
+      <c r="A16" s="62"/>
+      <c r="B16" s="59">
         <v>3</v>
       </c>
-      <c r="C16" s="36" t="s">
+      <c r="C16" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="38" t="s">
+      <c r="D16" s="61" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="38" t="s">
+      <c r="E16" s="61" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1" spans="1:5">
-      <c r="A17" s="39"/>
-      <c r="B17" s="35">
+      <c r="A17" s="62"/>
+      <c r="B17" s="59">
         <v>4</v>
       </c>
-      <c r="C17" s="36" t="s">
+      <c r="C17" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="38" t="s">
+      <c r="D17" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="38" t="s">
+      <c r="E17" s="61" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="18" ht="29" customHeight="1" spans="1:5">
-      <c r="A18" s="40" t="s">
+      <c r="A18" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="41">
+      <c r="B18" s="64">
         <v>1</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="42" t="s">
+      <c r="D18" s="65" t="s">
         <v>46</v>
       </c>
-      <c r="E18" s="43" t="s">
+      <c r="E18" s="66" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="19" ht="29" customHeight="1" spans="1:5">
-      <c r="A19" s="21"/>
-      <c r="B19" s="41">
+      <c r="A19" s="67"/>
+      <c r="B19" s="64">
         <v>2</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="43" t="s">
+      <c r="D19" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="E19" s="43" t="s">
+      <c r="E19" s="66" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="20" ht="29" customHeight="1" spans="1:5">
-      <c r="A20" s="21"/>
-      <c r="B20" s="41">
+      <c r="A20" s="67"/>
+      <c r="B20" s="64">
         <v>3</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="D20" s="43" t="s">
+      <c r="D20" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="E20" s="43" t="s">
+      <c r="E20" s="66" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1" spans="1:5">
-      <c r="A21" s="21"/>
-      <c r="B21" s="41">
+      <c r="A21" s="67"/>
+      <c r="B21" s="64">
         <v>4</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="D21" s="43" t="s">
+      <c r="D21" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="E21" s="43" t="s">
+      <c r="E21" s="66" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="22" ht="29" customHeight="1" spans="1:5">
-      <c r="A22" s="34" t="s">
+      <c r="A22" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="35">
+      <c r="B22" s="59">
         <v>1</v>
       </c>
-      <c r="C22" s="36" t="s">
+      <c r="C22" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="37" t="s">
+      <c r="D22" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="E22" s="38" t="s">
+      <c r="E22" s="61" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="23" ht="29" customHeight="1" spans="1:5">
-      <c r="A23" s="39"/>
-      <c r="B23" s="35">
+      <c r="A23" s="62"/>
+      <c r="B23" s="59">
         <v>2</v>
       </c>
-      <c r="C23" s="36" t="s">
+      <c r="C23" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D23" s="38" t="s">
+      <c r="D23" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="E23" s="38" t="s">
+      <c r="E23" s="61" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="24" ht="29" customHeight="1" spans="1:5">
-      <c r="A24" s="39"/>
-      <c r="B24" s="35">
+      <c r="A24" s="62"/>
+      <c r="B24" s="59">
         <v>3</v>
       </c>
-      <c r="C24" s="36" t="s">
+      <c r="C24" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="D24" s="38" t="s">
+      <c r="D24" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="E24" s="38" t="s">
+      <c r="E24" s="61" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="25" ht="42" customHeight="1" spans="1:5">
-      <c r="A25" s="39"/>
-      <c r="B25" s="35">
+      <c r="A25" s="62"/>
+      <c r="B25" s="59">
         <v>4</v>
       </c>
-      <c r="C25" s="36" t="s">
+      <c r="C25" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D25" s="38" t="s">
+      <c r="D25" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="E25" s="38" t="s">
-        <v>61</v>
+      <c r="E25" s="61" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="26" ht="29" customHeight="1" spans="1:5">
-      <c r="A26" s="40" t="s">
+      <c r="A26" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="41">
+      <c r="B26" s="64">
         <v>1</v>
       </c>
-      <c r="C26" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="D26" s="43" t="s">
+      <c r="C26" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E26" s="43" t="s">
+      <c r="D26" s="66" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26" s="66" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="27" ht="29" customHeight="1" spans="1:5">
-      <c r="A27" s="21"/>
-      <c r="B27" s="41">
+      <c r="A27" s="67"/>
+      <c r="B27" s="64">
         <v>2</v>
       </c>
-      <c r="C27" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="D27" s="42" t="s">
+      <c r="C27" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="E27" s="43" t="s">
+      <c r="D27" s="65" t="s">
+        <v>68</v>
+      </c>
+      <c r="E27" s="66" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="28" ht="60" customHeight="1" spans="1:5">
-      <c r="A28" s="21"/>
-      <c r="B28" s="41">
+      <c r="A28" s="67"/>
+      <c r="B28" s="64">
         <v>3</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="D28" s="66" t="s">
+        <v>47</v>
+      </c>
+      <c r="E28" s="66" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" ht="29" customHeight="1" spans="1:5">
+      <c r="A29" s="58" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" s="59">
+        <v>1</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" s="60" t="s">
+        <v>46</v>
+      </c>
+      <c r="E29" s="61" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" ht="29" customHeight="1" spans="1:5">
+      <c r="A30" s="62"/>
+      <c r="B30" s="59">
+        <v>2</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D30" s="61" t="s">
+        <v>72</v>
+      </c>
+      <c r="E30" s="61" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" ht="29" customHeight="1" spans="1:5">
+      <c r="A31" s="62"/>
+      <c r="B31" s="59">
+        <v>3</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D31" s="61" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" s="61" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" ht="42" customHeight="1" spans="1:5">
+      <c r="A32" s="62"/>
+      <c r="B32" s="59">
+        <v>4</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32" s="61" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" s="61" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33" ht="47" customHeight="1" spans="1:5">
+      <c r="A33" s="63" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" s="64">
+        <v>1</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="D33" s="66" t="s">
+        <v>49</v>
+      </c>
+      <c r="E33" s="66" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="34" ht="41" customHeight="1" spans="1:5">
+      <c r="A34" s="67"/>
+      <c r="B34" s="64">
+        <v>2</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="D34" s="66" t="s">
+        <v>77</v>
+      </c>
+      <c r="E34" s="66" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1" spans="1:5">
+      <c r="A35" s="67"/>
+      <c r="B35" s="64">
+        <v>3</v>
+      </c>
+      <c r="C35" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D35" s="66" t="s">
+        <v>80</v>
+      </c>
+      <c r="E35" s="66" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="36" ht="54" customHeight="1" spans="1:5">
+      <c r="A36" s="67"/>
+      <c r="B36" s="64">
+        <v>4</v>
+      </c>
+      <c r="C36" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="D36" s="65" t="s">
         <v>68</v>
       </c>
-      <c r="D28" s="43" t="s">
-        <v>47</v>
-      </c>
-      <c r="E28" s="43" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="29" ht="29" customHeight="1" spans="1:5">
-      <c r="A29" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="B29" s="35">
-        <v>1</v>
-      </c>
-      <c r="C29" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="D29" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="E29" s="38" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="30" ht="29" customHeight="1" spans="1:5">
-      <c r="A30" s="39"/>
-      <c r="B30" s="35">
-        <v>2</v>
-      </c>
-      <c r="C30" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="E30" s="38" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="31" ht="29" customHeight="1" spans="1:5">
-      <c r="A31" s="39"/>
-      <c r="B31" s="35">
-        <v>3</v>
-      </c>
-      <c r="C31" s="36" t="s">
-        <v>60</v>
-      </c>
-      <c r="D31" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="E31" s="38" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="32" ht="42" customHeight="1" spans="1:5">
-      <c r="A32" s="39"/>
-      <c r="B32" s="35">
-        <v>4</v>
-      </c>
-      <c r="C32" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="D32" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="E32" s="38" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="33" ht="47" customHeight="1" spans="1:5">
-      <c r="A33" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="B33" s="41">
-        <v>1</v>
-      </c>
-      <c r="C33" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="D33" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="E33" s="43" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="34" ht="41" customHeight="1" spans="1:5">
-      <c r="A34" s="21"/>
-      <c r="B34" s="41">
-        <v>2</v>
-      </c>
-      <c r="C34" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D34" s="43" t="s">
-        <v>76</v>
-      </c>
-      <c r="E34" s="43" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="35" ht="36" customHeight="1" spans="1:5">
-      <c r="A35" s="21"/>
-      <c r="B35" s="41">
-        <v>3</v>
-      </c>
-      <c r="C35" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="D35" s="43" t="s">
-        <v>79</v>
-      </c>
-      <c r="E35" s="43" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="36" ht="54" customHeight="1" spans="1:5">
-      <c r="A36" s="21"/>
-      <c r="B36" s="41">
-        <v>4</v>
-      </c>
-      <c r="C36" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="D36" s="42" t="s">
-        <v>67</v>
-      </c>
-      <c r="E36" s="43" t="s">
-        <v>82</v>
+      <c r="E36" s="66" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -2675,13 +3187,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="65" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="4" max="4" width="73.25" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="52" customWidth="1"/>
@@ -2701,7 +3213,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -2723,8 +3235,10 @@
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
     </row>
-    <row r="4" ht="11" customHeight="1" spans="1:7">
-      <c r="A4" s="8"/>
+    <row r="4" ht="23" customHeight="1" spans="1:7">
+      <c r="A4" s="8" t="s">
+        <v>85</v>
+      </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -2737,36 +3251,36 @@
         <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" ht="69" customHeight="1" spans="1:7">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" ht="31" customHeight="1" spans="1:7">
       <c r="A6" s="11" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E6" s="15"/>
       <c r="F6" s="16">
@@ -2774,74 +3288,58 @@
       </c>
       <c r="G6" s="15"/>
     </row>
-    <row r="7" ht="69" customHeight="1" spans="1:7">
-      <c r="A7" s="17" t="s">
+    <row r="7" ht="33" customHeight="1" spans="1:7">
+      <c r="A7" s="17"/>
+      <c r="B7" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="19"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="20"/>
+    </row>
+    <row r="8" ht="36" customHeight="1" spans="1:7">
+      <c r="A8" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B8" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="C7" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="E7" s="21"/>
-      <c r="F7" s="22">
+      <c r="D8" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" s="26"/>
+      <c r="F8" s="27">
         <v>46304</v>
       </c>
-      <c r="G7" s="21"/>
-    </row>
-    <row r="8" ht="58" customHeight="1" spans="1:7">
-      <c r="A8" s="11" t="s">
+      <c r="G8" s="26"/>
+    </row>
+    <row r="9" ht="39" customHeight="1" spans="1:7">
+      <c r="A9" s="28"/>
+      <c r="B9" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="29"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="30"/>
+    </row>
+    <row r="10" ht="39" customHeight="1" spans="1:7">
+      <c r="A10" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="D8" s="14" t="s">
+      <c r="B10" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="E8" s="15"/>
-      <c r="F8" s="16">
-        <v>46304</v>
-      </c>
-      <c r="G8" s="15"/>
-    </row>
-    <row r="9" ht="58" customHeight="1" spans="1:7">
-      <c r="A9" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="D9" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="E9" s="21"/>
-      <c r="F9" s="22">
-        <v>46304</v>
-      </c>
-      <c r="G9" s="21"/>
-    </row>
-    <row r="10" ht="58" customHeight="1" spans="1:7">
-      <c r="A10" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>95</v>
-      </c>
       <c r="C10" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="D10" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="D10" s="14" t="s">
         <v>99</v>
       </c>
       <c r="E10" s="15"/>
@@ -2850,118 +3348,308 @@
       </c>
       <c r="G10" s="15"/>
     </row>
-    <row r="11" ht="86" customHeight="1" spans="1:7">
-      <c r="A11" s="17" t="s">
-        <v>29</v>
-      </c>
+    <row r="11" ht="33" customHeight="1" spans="1:7">
+      <c r="A11" s="17"/>
       <c r="B11" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="C11" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="D11" s="20" t="s">
+      <c r="C11" s="19"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="20"/>
+    </row>
+    <row r="12" ht="33" customHeight="1" spans="1:7">
+      <c r="A12" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="D12" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="E11" s="21"/>
-      <c r="F11" s="22">
+      <c r="E12" s="26"/>
+      <c r="F12" s="27">
+        <v>46304</v>
+      </c>
+      <c r="G12" s="26"/>
+    </row>
+    <row r="13" ht="36" customHeight="1" spans="1:7">
+      <c r="A13" s="28"/>
+      <c r="B13" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" s="29"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="30"/>
+    </row>
+    <row r="14" ht="58" customHeight="1" spans="1:7">
+      <c r="A14" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="D14" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="E14" s="36"/>
+      <c r="F14" s="37">
+        <v>46304</v>
+      </c>
+      <c r="G14" s="36"/>
+    </row>
+    <row r="15" ht="43" customHeight="1" spans="1:7">
+      <c r="A15" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>106</v>
+      </c>
+      <c r="E15" s="26"/>
+      <c r="F15" s="27">
         <v>46305</v>
       </c>
-      <c r="G11" s="21"/>
-    </row>
-    <row r="12" ht="58" customHeight="1" spans="1:7">
-      <c r="A12" s="11" t="s">
+      <c r="G15" s="26"/>
+    </row>
+    <row r="16" ht="36" customHeight="1" spans="1:7">
+      <c r="A16" s="38"/>
+      <c r="B16" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="C16" s="39"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="40"/>
+    </row>
+    <row r="17" ht="40" customHeight="1" spans="1:7">
+      <c r="A17" s="28"/>
+      <c r="B17" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="29"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="30"/>
+    </row>
+    <row r="18" ht="42" customHeight="1" spans="1:7">
+      <c r="A18" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="E12" s="15"/>
-      <c r="F12" s="16">
+      <c r="B18" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E18" s="15"/>
+      <c r="F18" s="16">
         <v>46305</v>
       </c>
-      <c r="G12" s="15"/>
-    </row>
-    <row r="13" ht="245" customHeight="1" spans="1:7">
-      <c r="A13" s="17" t="s">
+      <c r="G18" s="15"/>
+    </row>
+    <row r="19" ht="41" customHeight="1" spans="1:7">
+      <c r="A19" s="42"/>
+      <c r="B19" s="43" t="s">
+        <v>110</v>
+      </c>
+      <c r="C19" s="44"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="45"/>
+    </row>
+    <row r="20" ht="55" customHeight="1" spans="1:7">
+      <c r="A20" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="D13" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="E13" s="21"/>
-      <c r="F13" s="22">
+      <c r="B20" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="E20" s="26"/>
+      <c r="F20" s="27">
         <v>46311</v>
       </c>
-      <c r="G13" s="21"/>
-    </row>
+      <c r="G20" s="26"/>
+    </row>
+    <row r="21" ht="52" customHeight="1" spans="1:7">
+      <c r="A21" s="38"/>
+      <c r="B21" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" s="39"/>
+      <c r="D21" s="47" t="s">
+        <v>114</v>
+      </c>
+      <c r="E21" s="40"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="40"/>
+    </row>
+    <row r="22" ht="51" customHeight="1" spans="1:7">
+      <c r="A22" s="38"/>
+      <c r="B22" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" s="39"/>
+      <c r="D22" s="47" t="s">
+        <v>116</v>
+      </c>
+      <c r="E22" s="40"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="40"/>
+    </row>
+    <row r="23" ht="39" customHeight="1" spans="1:7">
+      <c r="A23" s="38"/>
+      <c r="B23" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="C23" s="39"/>
+      <c r="D23" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="E23" s="40"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="40"/>
+    </row>
+    <row r="24" ht="49" customHeight="1" spans="1:7">
+      <c r="A24" s="28"/>
+      <c r="B24" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="C24" s="29"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="30"/>
+    </row>
+    <row r="25" ht="27" customHeight="1"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="47">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="E3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A24"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C20:C24"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="E20:E24"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="F20:F24"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="G20:G24"/>
   </mergeCells>
-  <conditionalFormatting sqref="C13">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
-      <formula>"PASS"</formula>
+  <conditionalFormatting sqref="C20">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"NEEDS CLARIFICATION"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
-      <formula>"FAIL"</formula>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"NOT RUN"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"BLOCKED"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
-      <formula>"NOT RUN"</formula>
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"FAIL"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C6 C8 C10 C12 C14:C15 C18">
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
       <formula>"NEEDS CLARIFICATION"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C6:C12">
-    <cfRule type="cellIs" dxfId="0" priority="10" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="9" operator="equal">
-      <formula>"FAIL"</formula>
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
+      <formula>"NOT RUN"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="2" priority="8" operator="equal">
       <formula>"BLOCKED"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
-      <formula>"NOT RUN"</formula>
+    <cfRule type="cellIs" dxfId="3" priority="9" operator="equal">
+      <formula>"FAIL"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
-      <formula>"NEEDS CLARIFICATION"</formula>
+    <cfRule type="cellIs" dxfId="4" priority="10" operator="equal">
+      <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="C6:C13">
+    <dataValidation type="list" sqref="C6:C20">
       <formula1>"PASS,FAIL,BLOCKED,NOT RUN,NEEDS CLARIFICATION"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D12" r:id="rId1" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-007_PASS.png" tooltip="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-007_PASS.png"/>
-    <hyperlink ref="D11" r:id="rId2" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-006_PASS.png" tooltip="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-006_PASS.png"/>
-    <hyperlink ref="D10" r:id="rId3" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-005_PASS.png" tooltip="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-005_PASS.png"/>
-    <hyperlink ref="D9" r:id="rId4" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-004_PASS.png"/>
-    <hyperlink ref="D8" r:id="rId5" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-003_PASS.png"/>
-    <hyperlink ref="D7" r:id="rId6" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-002_PASS.png" tooltip="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-002_PASS.png"/>
+    <hyperlink ref="D18" r:id="rId1" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-007_PASS.png" tooltip="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-007_PASS.png"/>
+    <hyperlink ref="D15" r:id="rId2" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-006_PASS.png" tooltip="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-006_PASS.png"/>
+    <hyperlink ref="D14" r:id="rId3" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-005_PASS.png" tooltip="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-005_PASS.png"/>
+    <hyperlink ref="D12" r:id="rId4" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-004_PASS.png"/>
+    <hyperlink ref="D10" r:id="rId5" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-003_PASS.png"/>
+    <hyperlink ref="D8" r:id="rId6" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-002_PASS.png" tooltip="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-002_PASS.png"/>
     <hyperlink ref="D6" r:id="rId7" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-001_PASS.png" tooltip="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-001_PASS.png"/>
-    <hyperlink ref="D13" r:id="rId8" display="1. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-008_01_PRODUCTS.png&#10;&#10;2. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-008_02_MENU.png&#10;&#10;3. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-008_03_LOGIN.png&#10;&#10;4. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-008_04_ACCESS_BLOCKED.png"/>
+    <hyperlink ref="D20" r:id="rId8" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-008_01_PRODUCTS.png"/>
+    <hyperlink ref="D21" r:id="rId9" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-008_02_MENU.png"/>
+    <hyperlink ref="D22" r:id="rId10" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-008_03_LOGIN.png"/>
+    <hyperlink ref="D23" r:id="rId11" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/login/TC-LOGIN-008_04_ACCESS_BLOCKED.png"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
